--- a/backend/preview.xlsx
+++ b/backend/preview.xlsx
@@ -10,7 +10,7 @@
     <sheet sheetId="10" name="Planilla" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Planilla'!$A2:$G32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Planilla'!$A2:$G33</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Planilla'!$1:$9</definedName>
   </definedNames>
   <calcPr calcId="171027"/>
@@ -18,12 +18,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="46">
   <si>
     <t>OBJETO DE COMPRA:</t>
   </si>
   <si>
-    <t>OBJETO DE COMPRA: CM-PROF-PREVIEW PROFORMA VISTA PREVIA DE DISEÑO Y BORDES</t>
+    <t>CM-PROF-PREVIEW - VISTA PREVIA DE DISEÑO Y BORDES</t>
   </si>
   <si>
     <t>RAZÓN SOCIAL: CONSTRUMÉTRICA INGENIEROS METRICAASOCIADOS CIA. LTDA.</t>
@@ -66,6 +66,9 @@
   </si>
   <si>
     <t>TIEMPO DE ENTREGA:</t>
+  </si>
+  <si>
+    <t>FECHA DE LA OFERTA:</t>
   </si>
   <si>
     <t>11 de agosto de 2026</t>
@@ -192,6 +195,22 @@
       <name val="Gotham"/>
     </font>
     <font>
+      <color rgb="FF000000"/>
+      <sz val="12"/>
+      <name val="Gotham"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Gotham Black"/>
+    </font>
+    <font>
+      <color rgb="FF000000"/>
+      <sz val="12"/>
+      <name val="Gotham Black"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF000000"/>
       <sz val="12"/>
       <name val="Gotham Black"/>
     </font>
@@ -206,7 +225,8 @@
       <name val="Gotham"/>
     </font>
     <font>
-      <color rgb="FFFF0000"/>
+      <b/>
+      <color rgb="FFFF0033"/>
       <sz val="12"/>
       <name val="Gotham Black"/>
     </font>
@@ -237,25 +257,9 @@
       <name val="Gotham Black"/>
     </font>
     <font>
-      <color rgb="FF444242"/>
-      <sz val="12"/>
-      <name val="Gotham Book"/>
-    </font>
-    <font>
       <color rgb="FFFF0033"/>
       <sz val="12"/>
-      <name val="Gotham Book"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF444242"/>
-      <sz val="12"/>
       <name val="Gotham Black"/>
-    </font>
-    <font>
-      <color rgb="FF777777"/>
-      <sz val="12"/>
-      <name val="Gotham Book"/>
     </font>
   </fonts>
   <fills count="5">
@@ -598,7 +602,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -639,53 +643,53 @@
     <xf numFmtId="1" fontId="5" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="4" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="6" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
@@ -695,95 +699,98 @@
     <xf numFmtId="9" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="14" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="14" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="14" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="5" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -817,9 +824,9 @@
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>19007</xdr:colOff>
+      <xdr:colOff>300000</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>111000</xdr:rowOff>
+      <xdr:rowOff>70000</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1571625" cy="495300"/>
     <xdr:pic>
@@ -856,11 +863,11 @@
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>100000</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>108000</xdr:rowOff>
+      <xdr:colOff>500000</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1771650" cy="1771650"/>
+    <xdr:ext cx="1524000" cy="1524000"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Picture 2">
@@ -1246,8 +1253,8 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
-  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="11.453125" customHeight="1"/>
+  <dimension ref="A1:G38"/>
+  <sheetFormatPr defaultRowHeight="15.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="11.453125" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="17.26953125" style="1" customWidth="1"/>
     <col min="2" max="2" width="65.81640625" style="1" customWidth="1"/>
@@ -1358,7 +1365,7 @@
       </c>
       <c r="B8" s="23"/>
       <c r="C8" s="26">
-        <f>+G19</f>
+        <f>+G20</f>
       </c>
       <c r="D8" s="26"/>
       <c r="E8" s="26"/>
@@ -1371,144 +1378,142 @@
       </c>
       <c r="B9" s="29"/>
       <c r="C9" s="30">
-        <f>C16&amp;" "&amp;"Días Laborables"</f>
+        <f>C17&amp;" "&amp;"Días Laborables"</f>
       </c>
       <c r="D9" s="30"/>
       <c r="E9" s="30"/>
       <c r="F9" s="31"/>
       <c r="G9" s="32"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="33"/>
-      <c r="B10" s="34"/>
-      <c r="C10" s="35" t="s">
+    <row r="10" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="35"/>
-      <c r="E10" s="36"/>
-      <c r="F10" s="36"/>
-      <c r="G10" s="37"/>
-    </row>
-    <row r="11" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="38" t="s">
+      <c r="B10" s="29"/>
+      <c r="C10" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="39" t="s">
+      <c r="D10" s="30"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="32"/>
+    </row>
+    <row r="11" ht="16" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="34"/>
+      <c r="B11" s="35"/>
+      <c r="C11" s="36"/>
+      <c r="D11" s="36"/>
+      <c r="E11" s="37"/>
+      <c r="F11" s="37"/>
+      <c r="G11" s="38"/>
+    </row>
+    <row r="12" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="39" t="s">
+      <c r="B12" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="D11" s="39" t="s">
+      <c r="C12" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="39" t="s">
+      <c r="D12" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="F11" s="39"/>
-      <c r="G11" s="40"/>
-    </row>
-    <row r="12" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="41"/>
-      <c r="B12" s="42"/>
-      <c r="C12" s="42" t="s">
+      <c r="E12" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="42"/>
-      <c r="E12" s="42" t="s">
+      <c r="F12" s="40"/>
+      <c r="G12" s="41"/>
+    </row>
+    <row r="13" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="42"/>
+      <c r="B13" s="43"/>
+      <c r="C13" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="F12" s="42" t="s">
+      <c r="D13" s="43"/>
+      <c r="E13" s="43" t="s">
         <v>24</v>
       </c>
-      <c r="G12" s="43" t="s">
+      <c r="F13" s="43" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="13" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="44" t="s">
+      <c r="G13" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="44"/>
-      <c r="C13" s="44"/>
-      <c r="D13" s="44"/>
-      <c r="E13" s="44"/>
-      <c r="F13" s="44"/>
-      <c r="G13" s="44"/>
-    </row>
-    <row r="14" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="45" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="46" t="s">
+      <c r="B14" s="45"/>
+      <c r="C14" s="45"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="45"/>
+      <c r="G14" s="45"/>
+    </row>
+    <row r="15" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="46" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="47">
+      <c r="B15" s="47" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="48">
         <v>3</v>
       </c>
-      <c r="D14" s="47" t="s">
-        <v>29</v>
-      </c>
-      <c r="E14" s="48">
+      <c r="D15" s="48" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" s="49">
         <v>150</v>
       </c>
-      <c r="F14" s="49">
+      <c r="F15" s="50">
         <v>2.5</v>
       </c>
-      <c r="G14" s="50">
-        <f>E14*F14</f>
-      </c>
-    </row>
-    <row r="15" ht="45" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="45" t="s">
-        <v>30</v>
-      </c>
-      <c r="B15" s="46" t="s">
+      <c r="G15" s="51">
+        <f>E15*F15</f>
+      </c>
+    </row>
+    <row r="16" ht="45" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="C15" s="47">
+      <c r="B16" s="47" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="48">
         <v>5</v>
       </c>
-      <c r="D15" s="47" t="s">
-        <v>32</v>
-      </c>
-      <c r="E15" s="48">
+      <c r="D16" s="48" t="s">
+        <v>33</v>
+      </c>
+      <c r="E16" s="49">
         <v>45</v>
       </c>
-      <c r="F15" s="49">
+      <c r="F16" s="50">
         <v>12</v>
       </c>
-      <c r="G15" s="50">
-        <f>E15*F15</f>
-      </c>
-    </row>
-    <row r="16" ht="16" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="33"/>
-      <c r="B16" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16" s="52">
-        <f>SUM(C14,C15)</f>
-      </c>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="53"/>
+      <c r="G16" s="51">
+        <f>E16*F16</f>
+      </c>
     </row>
     <row r="17" ht="16" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="54" t="s">
+      <c r="A17" s="34"/>
+      <c r="B17" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="B17" s="54"/>
-      <c r="C17" s="54"/>
-      <c r="D17" s="54"/>
-      <c r="E17" s="54"/>
-      <c r="F17" s="54"/>
-      <c r="G17" s="55">
-        <f>SUM(G14,G15)</f>
-      </c>
-    </row>
-    <row r="18" ht="10.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C17" s="48">
+        <f>SUM(C15,C16)</f>
+      </c>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="53"/>
+    </row>
+    <row r="18" ht="16" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="54" t="s">
         <v>35</v>
       </c>
@@ -1518,52 +1523,54 @@
       <c r="E18" s="54"/>
       <c r="F18" s="54"/>
       <c r="G18" s="55">
-        <f>0.15*G17</f>
-      </c>
-    </row>
-    <row r="19" ht="16" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="56" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19" s="56"/>
-      <c r="C19" s="56"/>
-      <c r="D19" s="56"/>
-      <c r="E19" s="56"/>
-      <c r="F19" s="56"/>
-      <c r="G19" s="57">
-        <f>G17+G18</f>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="33"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="53"/>
+        <f>SUM(G15,G16)</f>
+      </c>
+    </row>
+    <row r="19" ht="10.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="54" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" s="54"/>
+      <c r="C19" s="54"/>
+      <c r="D19" s="54"/>
+      <c r="E19" s="54"/>
+      <c r="F19" s="54"/>
+      <c r="G19" s="55">
+        <f>0.15*G18</f>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="56" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="56"/>
+      <c r="C20" s="56"/>
+      <c r="D20" s="56"/>
+      <c r="E20" s="56"/>
+      <c r="F20" s="56"/>
+      <c r="G20" s="57">
+        <f>G18+G19</f>
+      </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="B21" s="58"/>
-      <c r="C21" s="58"/>
-      <c r="D21" s="58"/>
-      <c r="E21" s="58"/>
-      <c r="F21" s="58"/>
-      <c r="G21" s="58"/>
-    </row>
-    <row r="22" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="59" t="s">
+      <c r="A21" s="34"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="53"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="59"/>
-      <c r="C22" s="59"/>
-      <c r="D22" s="59"/>
-      <c r="E22" s="59"/>
-      <c r="F22" s="59"/>
-      <c r="G22" s="59"/>
+      <c r="B22" s="58"/>
+      <c r="C22" s="58"/>
+      <c r="D22" s="58"/>
+      <c r="E22" s="58"/>
+      <c r="F22" s="58"/>
+      <c r="G22" s="58"/>
     </row>
     <row r="23" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="59" t="s">
@@ -1576,17 +1583,19 @@
       <c r="F23" s="59"/>
       <c r="G23" s="59"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="33"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="53"/>
+    <row r="24" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="59" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="59"/>
+      <c r="C24" s="59"/>
+      <c r="D24" s="59"/>
+      <c r="E24" s="59"/>
+      <c r="F24" s="59"/>
+      <c r="G24" s="59"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="33"/>
+      <c r="A25" s="34"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
@@ -1595,7 +1604,7 @@
       <c r="G25" s="53"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="33"/>
+      <c r="A26" s="34"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
@@ -1604,7 +1613,7 @@
       <c r="G26" s="53"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="33"/>
+      <c r="A27" s="34"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
@@ -1612,8 +1621,8 @@
       <c r="F27" s="1"/>
       <c r="G27" s="53"/>
     </row>
-    <row r="28" ht="15.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="33"/>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="34"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
@@ -1621,8 +1630,8 @@
       <c r="F28" s="1"/>
       <c r="G28" s="53"/>
     </row>
-    <row r="29" ht="16" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="33"/>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="34"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
@@ -1631,17 +1640,15 @@
       <c r="G29" s="53"/>
     </row>
     <row r="30" ht="16" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="58" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="58"/>
-      <c r="C30" s="58"/>
-      <c r="D30" s="58"/>
-      <c r="E30" s="58"/>
-      <c r="F30" s="58"/>
-      <c r="G30" s="58"/>
-    </row>
-    <row r="31" ht="15.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="34"/>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="53"/>
+    </row>
+    <row r="31" ht="16" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="60" t="s">
         <v>40</v>
       </c>
@@ -1652,62 +1659,73 @@
       <c r="F31" s="60"/>
       <c r="G31" s="60"/>
     </row>
-    <row r="32" ht="16" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="60" t="s">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="61" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="60"/>
-      <c r="C32" s="60"/>
-      <c r="D32" s="60"/>
-      <c r="E32" s="60"/>
-      <c r="F32" s="60"/>
-      <c r="G32" s="60"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="60" t="s">
+      <c r="B32" s="61"/>
+      <c r="C32" s="61"/>
+      <c r="D32" s="61"/>
+      <c r="E32" s="61"/>
+      <c r="F32" s="61"/>
+      <c r="G32" s="61"/>
+    </row>
+    <row r="33" ht="16" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="61" t="s">
         <v>42</v>
       </c>
-      <c r="B33" s="60"/>
-      <c r="C33" s="60"/>
-      <c r="D33" s="60"/>
-      <c r="E33" s="60"/>
-      <c r="F33" s="60"/>
-      <c r="G33" s="60"/>
+      <c r="B33" s="61"/>
+      <c r="C33" s="61"/>
+      <c r="D33" s="61"/>
+      <c r="E33" s="61"/>
+      <c r="F33" s="61"/>
+      <c r="G33" s="61"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="60" t="s">
+      <c r="A34" s="61" t="s">
         <v>43</v>
       </c>
-      <c r="B34" s="60"/>
-      <c r="C34" s="60"/>
-      <c r="D34" s="60"/>
-      <c r="E34" s="60"/>
-      <c r="F34" s="60"/>
-      <c r="G34" s="60"/>
+      <c r="B34" s="61"/>
+      <c r="C34" s="61"/>
+      <c r="D34" s="61"/>
+      <c r="E34" s="61"/>
+      <c r="F34" s="61"/>
+      <c r="G34" s="61"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="60" t="s">
+      <c r="A35" s="61" t="s">
         <v>44</v>
       </c>
-      <c r="B35" s="60"/>
-      <c r="C35" s="60"/>
-      <c r="D35" s="60"/>
-      <c r="E35" s="60"/>
-      <c r="F35" s="60"/>
-      <c r="G35" s="60"/>
+      <c r="B35" s="61"/>
+      <c r="C35" s="61"/>
+      <c r="D35" s="61"/>
+      <c r="E35" s="61"/>
+      <c r="F35" s="61"/>
+      <c r="G35" s="61"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="61"/>
-      <c r="B36" s="62"/>
-      <c r="C36" s="62"/>
-      <c r="D36" s="62"/>
-      <c r="E36" s="62"/>
-      <c r="F36" s="62"/>
-      <c r="G36" s="63"/>
-    </row>
-    <row r="37" ht="15.5" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="A36" s="61" t="s">
+        <v>45</v>
+      </c>
+      <c r="B36" s="61"/>
+      <c r="C36" s="61"/>
+      <c r="D36" s="61"/>
+      <c r="E36" s="61"/>
+      <c r="F36" s="61"/>
+      <c r="G36" s="61"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="62"/>
+      <c r="B37" s="63"/>
+      <c r="C37" s="63"/>
+      <c r="D37" s="63"/>
+      <c r="E37" s="63"/>
+      <c r="F37" s="63"/>
+      <c r="G37" s="64"/>
+    </row>
+    <row r="38" ht="15.5" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="25">
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="E3:G3"/>
@@ -1715,23 +1733,24 @@
     <mergeCell ref="C6:E6"/>
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="C9:E9"/>
-    <mergeCell ref="E11:G11"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="A14:G14"/>
     <mergeCell ref="A18:F18"/>
     <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A20:F20"/>
     <mergeCell ref="A22:G22"/>
     <mergeCell ref="A23:G23"/>
-    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="A24:G24"/>
     <mergeCell ref="A31:G31"/>
     <mergeCell ref="A32:G32"/>
     <mergeCell ref="A33:G33"/>
     <mergeCell ref="A34:G34"/>
     <mergeCell ref="A35:G35"/>
+    <mergeCell ref="A36:G36"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.23622047244094488" right="0.23622047244094488" top="0.28" bottom="4.68" header="0.31496062992125984" footer="0.31496062992125984"/>
